--- a/パズルボブル進捗シート.xlsx
+++ b/パズルボブル進捗シート.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>パズルボブル</t>
   </si>
@@ -118,15 +118,6 @@
     <t>発射台の少し左に”NEXT"の文字があり、その下に次の玉が表示</t>
   </si>
   <si>
-    <t>１３</t>
-  </si>
-  <si>
-    <t>スコア計算</t>
-  </si>
-  <si>
-    <t>玉を消した、巻き込んで落とした時にスコア加算</t>
-  </si>
-  <si>
     <t>１４</t>
   </si>
   <si>
@@ -134,15 +125,6 @@
   </si>
   <si>
     <t>時間経過か打った玉によって上の壁が段階的に下りてくる</t>
-  </si>
-  <si>
-    <t>１５</t>
-  </si>
-  <si>
-    <t>クリア判定</t>
-  </si>
-  <si>
-    <t>玉をすべて消すとクリア</t>
   </si>
 </sst>
 </file>
@@ -191,7 +173,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border/>
     <border>
       <left style="thin">
@@ -345,51 +327,52 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFF6F8F9"/>
+      </left>
+      <top style="thin">
+        <color rgb="FFF6F8F9"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFF6F8F9"/>
+      </top>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF284E3F"/>
       </right>
       <top style="thin">
         <color rgb="FFF6F8F9"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
       <right style="thin">
-        <color rgb="FF284E3F"/>
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -407,43 +390,49 @@
     <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="6" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="7" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="10" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="14" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="17" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="17" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="19" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="20" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -696,31 +685,31 @@
         <v>3</v>
       </c>
       <c r="C3" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="6"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="C4" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
@@ -730,31 +719,31 @@
         <v>9</v>
       </c>
       <c r="C5" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="21"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15" t="s">
+      <c r="C6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
@@ -764,31 +753,31 @@
         <v>15</v>
       </c>
       <c r="C7" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15" t="s">
+      <c r="C8" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
@@ -798,31 +787,31 @@
         <v>21</v>
       </c>
       <c r="C9" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="15" t="s">
+      <c r="C10" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
     </row>
     <row r="11">
       <c r="A11" s="7">
@@ -832,31 +821,31 @@
         <v>26</v>
       </c>
       <c r="C11" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="21"/>
     </row>
     <row r="12">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>10.0</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="13">
       <c r="A13" s="7">
@@ -866,31 +855,31 @@
         <v>30</v>
       </c>
       <c r="C13" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="21"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="23" t="s">
+      <c r="C14" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="24"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="26"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
@@ -900,51 +889,17 @@
         <v>36</v>
       </c>
       <c r="C15" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="17"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="27"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="14">
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="D4:G4"/>
@@ -952,8 +907,6 @@
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="D8:G8"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="D11:G11"/>
